--- a/data/processed/companies_clean.xlsx
+++ b/data/processed/companies_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Narendra\Desktop\nifty100_project\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F08BFC2-B031-4E80-8EDB-ACA386A4D641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AAEEC8-A5A6-4E67-93AE-60C66DDD55D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="704">
   <si>
     <t>id</t>
   </si>
@@ -2192,6 +2192,9 @@
   </si>
   <si>
     <t>roe_percentage</t>
+  </si>
+  <si>
+    <t>company_id</t>
   </si>
 </sst>
 </file>
@@ -2222,12 +2225,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -2238,9 +2256,12 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2546,3975 +2567,4269 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C1" t="s">
         <v>93</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>184</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>277</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>331</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>424</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>515</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>607</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>699</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>700</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>701</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>332</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1657</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>46</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>34.9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>333</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>175</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>9</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>8.59</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>334</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>363</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>11.6</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>13.64</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>335</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>10</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>67</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>96.5</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>14.7</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>336</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>265</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>12.9</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>337</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>145</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>32.200000000000003</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>57.1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>338</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>2</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>205</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>12.8</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>9.24</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>339</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>5</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>522</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>17.2</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>13.81</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>340</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>1</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>188</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>41.75</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>31.45</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>341</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>36</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>21.2</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>20.5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>195</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>342</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>509</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>7.06</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>343</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>10</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>1109</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>33.5</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>26.5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>197</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>344</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>1</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>428</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>21.14</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>11.72</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>345</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>10</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>5375</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>13.1</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>14.8</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>346</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>2</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>1402</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>11.9</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>22.1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>347</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>2</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>231</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>6.33</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>16.7</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>201</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>348</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>1</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>24</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>34.6</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>26.3</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>202</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>349</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>5</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>153</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>13.1</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>14.9</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>203</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>350</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>2</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>70</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>3.28</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>1.05</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>204</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>351</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>10</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>4319</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>20.6</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>205</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>352</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>10</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>178</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>32.1</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>41.9</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>206</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>353</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>1</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>133</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>48.9</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>57.1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>207</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>354</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>2</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>102</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>6.63</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>208</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>355</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>2</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>255</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>10.4</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>20.2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>209</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>356</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>2</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>351</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>22.8</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>16.8</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>210</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>357</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>10</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>156</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>63.6</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>211</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>358</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>59</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>22.3</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>19.2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>212</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>359</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>2</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>517</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>16.5</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>12.2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>213</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>360</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>2</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>163</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>5.74</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>6.95</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>214</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>361</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>10</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>309</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>19.399999999999999</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>14.5</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>215</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>362</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>1</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>369</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>26.5</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>21.4</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>216</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>363</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>1</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>693</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>31.1</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>24.2</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>217</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>364</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>10</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>127</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>14.7</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>218</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>365</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>1</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>119</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>26.49</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>6.77</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>219</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>366</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>2</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>1411</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>9.3000000000000007</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>6.9</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>220</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>367</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>5</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>465</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>38.9</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>28.9</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>221</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>368</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>1</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>124</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>24.4</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>222</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>369</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>2</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>254</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>29.6</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>23.3</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>223</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>370</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>1</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>601</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>7.67</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>224</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>371</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>10</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>73</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>6.61</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>11.4</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>225</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>372</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>2</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>951</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>29.1</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>226</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>373</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>1</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>153</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>11.3</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>227</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>374</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>1</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>216</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>27.2</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>20.2</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>228</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>375</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>2</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>365</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>7.6</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>18.8</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>229</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>376</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>10</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>275</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>22.5</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>230</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>377</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>10</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>80</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>8.75</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>8.07</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>231</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>378</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>10</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>97</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>24.5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>232</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>379</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>10</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>807</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>7.93</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>15.2</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>233</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>380</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>5</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>218</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>40</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>31.8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>234</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>381</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>10</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>129</v>
       </c>
-      <c r="K51">
+      <c r="L51">
         <v>21.31</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>25.44</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>235</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>382</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>2</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>44</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>53.8</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>40.4</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>236</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>383</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>10</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>39</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>5.73</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>13.7</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>237</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>384</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>1</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>60</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>34.76</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>29.47</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>238</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>385</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>1</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>464</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>13.2</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>14.1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>239</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>386</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="I56" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>10</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>216</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>2.16</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>1.82</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>240</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>387</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>10</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>160</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>8.59</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>8.4</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>241</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>388</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>1</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>326</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>13.36</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>11.66</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>242</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>389</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="I59" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>5</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>654</v>
       </c>
-      <c r="K59">
+      <c r="L59">
         <v>7.86</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>15.1</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>243</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>390</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="I60" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>10</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>154</v>
       </c>
-      <c r="K60">
+      <c r="L60">
         <v>63.79</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>63.61</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>244</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>391</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>10</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>183</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>11.1</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>10.7</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>245</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>392</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>2</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>635</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>17.18</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>10.49</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63">
         <v>62</v>
       </c>
-      <c r="C63" t="s">
+      <c r="B63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" t="s">
         <v>246</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>393</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="G63" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="H63" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>1</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>711</v>
       </c>
-      <c r="K63">
+      <c r="L63">
         <v>34.1</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>26.04</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>247</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>394</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="I64" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>5</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>567</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>26.98</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>248</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>395</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>5</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>2835</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>23.67</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>15.75</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>249</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>396</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="H66" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="I66" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>1</v>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>46</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>13.7</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>11.8</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>250</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>397</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="H67" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>10</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>3225</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>3.65</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>2.44</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>251</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>398</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>1</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>41</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>185.43</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>135.61000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>399</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>10</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>40</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>7.67</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>9.61</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>253</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>400</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>10</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>174</v>
       </c>
-      <c r="K70">
+      <c r="L70">
         <v>10.58</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>12.52</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>254</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>401</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="I71" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>5</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>275</v>
       </c>
-      <c r="K71">
+      <c r="L71">
         <v>19.71</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>14.32</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>255</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>402</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="I72" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>10</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>333</v>
       </c>
-      <c r="K72">
+      <c r="L72">
         <v>9.9600000000000009</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>19.489999999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" t="s">
+        <v>72</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>256</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>403</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="H73" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>1</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>171</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>29.7</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>22.8</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>257</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>404</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="I74" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>2</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>110</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <v>1.63</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>258</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>405</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>10</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>99</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <v>13.2</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>259</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>406</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="I76" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="I76">
+      <c r="J76">
         <v>10</v>
       </c>
-      <c r="J76">
+      <c r="K76">
         <v>279</v>
       </c>
-      <c r="K76">
+      <c r="L76">
         <v>10</v>
       </c>
-      <c r="L76">
+      <c r="M76">
         <v>22.2</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>260</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>407</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="I77">
+      <c r="J77">
         <v>10</v>
       </c>
-      <c r="J77">
+      <c r="K77">
         <v>606</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>9.61</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>9.25</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>261</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>408</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="G78" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="I78">
+      <c r="J78">
         <v>10</v>
       </c>
-      <c r="J78">
+      <c r="K78">
         <v>162</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>13.2</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>262</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>409</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="I79">
+      <c r="J79">
         <v>1</v>
       </c>
-      <c r="J79">
+      <c r="K79">
         <v>465</v>
       </c>
-      <c r="K79">
+      <c r="L79">
         <v>6.16</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>17.3</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>263</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>410</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="I80" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="I80">
+      <c r="J80">
         <v>10</v>
       </c>
-      <c r="J80">
+      <c r="K80">
         <v>5787</v>
       </c>
-      <c r="K80">
+      <c r="L80">
         <v>14.8</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>12.2</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>264</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>411</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="H81" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="I81">
+      <c r="J81">
         <v>2</v>
       </c>
-      <c r="J81">
+      <c r="K81">
         <v>279</v>
       </c>
-      <c r="K81">
+      <c r="L81">
         <v>11.3</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>15.9</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>265</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>412</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="I82">
+      <c r="J82">
         <v>2</v>
       </c>
-      <c r="J82">
+      <c r="K82">
         <v>431</v>
       </c>
-      <c r="K82">
+      <c r="L82">
         <v>25.6</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" t="s">
+        <v>82</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>266</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>413</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="G83" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="H83" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="I83" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="I83">
+      <c r="J83">
         <v>1</v>
       </c>
-      <c r="J83">
+      <c r="K83">
         <v>288</v>
       </c>
-      <c r="K83">
+      <c r="L83">
         <v>17.3</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>16.7</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>267</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>414</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="I84" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="I84">
+      <c r="J84">
         <v>1</v>
       </c>
-      <c r="J84">
+      <c r="K84">
         <v>193</v>
       </c>
-      <c r="K84">
+      <c r="L84">
         <v>10.6</v>
       </c>
-      <c r="L84">
+      <c r="M84">
         <v>8.32</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>268</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>415</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="I85">
+      <c r="J85">
         <v>2</v>
       </c>
-      <c r="J85">
+      <c r="K85">
         <v>275</v>
       </c>
-      <c r="K85">
+      <c r="L85">
         <v>20.100000000000001</v>
       </c>
-      <c r="L85">
+      <c r="M85">
         <v>49.4</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" t="s">
+        <v>85</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>269</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>416</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="H86" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="I86" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="I86">
+      <c r="J86">
         <v>1</v>
       </c>
-      <c r="J86">
+      <c r="K86">
         <v>105</v>
       </c>
-      <c r="K86">
+      <c r="L86">
         <v>11.1</v>
       </c>
-      <c r="L86">
+      <c r="M86">
         <v>11.3</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>270</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>417</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="G87" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="H87" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="I87">
+      <c r="J87">
         <v>1</v>
       </c>
-      <c r="J87">
+      <c r="K87">
         <v>72</v>
       </c>
-      <c r="K87">
+      <c r="L87">
         <v>7.02</v>
       </c>
-      <c r="L87">
+      <c r="M87">
         <v>6.55</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>271</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>418</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="G88" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="I88">
+      <c r="J88">
         <v>1</v>
       </c>
-      <c r="J88">
+      <c r="K88">
         <v>281</v>
       </c>
-      <c r="K88">
+      <c r="L88">
         <v>64.3</v>
       </c>
-      <c r="L88">
+      <c r="M88">
         <v>0.52</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>272</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>419</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="H89" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="I89" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="I89">
+      <c r="J89">
         <v>5</v>
       </c>
-      <c r="J89">
+      <c r="K89">
         <v>270</v>
       </c>
-      <c r="K89">
+      <c r="L89">
         <v>11.9</v>
       </c>
-      <c r="L89">
+      <c r="M89">
         <v>8.6300000000000008</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>273</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>420</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="G90" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="I90">
+      <c r="J90">
         <v>1</v>
       </c>
-      <c r="J90">
+      <c r="K90">
         <v>110</v>
       </c>
-      <c r="K90">
+      <c r="L90">
         <v>22.7</v>
       </c>
-      <c r="L90">
+      <c r="M90">
         <v>32.9</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>274</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>421</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="G91" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="H91" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="I91" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="I91">
+      <c r="J91">
         <v>5</v>
       </c>
-      <c r="J91">
+      <c r="K91">
         <v>222</v>
       </c>
-      <c r="K91">
+      <c r="L91">
         <v>23.2</v>
       </c>
-      <c r="L91">
+      <c r="M91">
         <v>24.2</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>275</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>422</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="G92" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="H92" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="I92" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="I92">
+      <c r="J92">
         <v>1</v>
       </c>
-      <c r="J92">
+      <c r="K92">
         <v>132</v>
       </c>
-      <c r="K92">
+      <c r="L92">
         <v>23.8</v>
       </c>
-      <c r="L92">
+      <c r="M92">
         <v>27.2</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" t="s">
+        <v>92</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>276</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>423</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H2" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D3" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="F3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G3" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B4" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D4" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F4" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G4" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H4" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B5" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D5" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F5" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G5" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H5" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B6" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D6" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F6" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="G6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="H6" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B7" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D7" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F7" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="G7" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="H7" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B8" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D8" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F8" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="G8" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="H8" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="B9" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D9" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F9" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="G9" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H9" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B10" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="D10" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F10" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="G10" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="H10" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B11" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D11" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F11" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="G11" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="H11" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B12" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D12" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F12" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="G12" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H12" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B13" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D13" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F13" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="G13" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="H13" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B14" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D14" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F14" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="G14" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="H14" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B15" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D15" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F15" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="G15" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="H15" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B16" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D16" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F16" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="G16" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="H16" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B17" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D17" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F17" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="G17" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="H17" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B18" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D18" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F18" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="G18" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="H18" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B19" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D19" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F19" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="G19" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="H19" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B20" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D20" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="F20" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="G20" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="H20" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="B21" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D21" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F21" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="G21" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="H21" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="B22" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D22" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="F22" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="G22" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="H22" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B23" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D23" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F23" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="G23" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="H23" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B24" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D24" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F24" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="G24" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="H24" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B25" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D25" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F25" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="G25" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="H25" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="B26" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D26" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="F26" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="G26" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="H26" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="B27" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D27" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="F27" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="G27" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="H27" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="B28" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D28" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F28" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="G28" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="H28" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="B29" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D29" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F29" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="G29" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="H29" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="B30" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D30" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F30" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="G30" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="H30" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="B31" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D31" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="F31" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="G31" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="H31" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="B32" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D32" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="F32" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="G32" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="H32" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="B33" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D33" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="F33" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="G33" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="H33" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="B34" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D34" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="F34" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="G34" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="H34" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="B35" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D35" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="F35" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="G35" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="H35" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="B36" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D36" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="F36" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="G36" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="H36" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="B37" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D37" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="F37" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="G37" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="H37" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="B38" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D38" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="F38" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="G38" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="H38" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="B39" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D39" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="F39" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="G39" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="H39" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="B40" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D40" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="F40" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="G40" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="H40" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="B41" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D41" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="F41" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="G41" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="H41" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="B42" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D42" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="F42" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="G42" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="H42" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="B43" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="D43" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="F43" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="G43" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="H43" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="B44" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="D44" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="F44" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="G44" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="H44" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="B45" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="D45" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="F45" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="G45" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="H45" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="B46" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="D46" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="F46" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="G46" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="H46" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="B47" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="D47" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="F47" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="G47" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="H47" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="B48" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="D48" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="F48" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="G48" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="H48" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="B49" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="D49" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="F49" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="G49" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="H49" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="B50" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="D50" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="F50" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="G50" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="H50" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="B51" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="D51" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="F51" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="G51" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="H51" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="B52" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="D52" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="F52" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="G52" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="H52" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="B53" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="D53" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="F53" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="G53" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="H53" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="B54" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="D54" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="F54" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="G54" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="H54" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="B55" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="D55" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="F55" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="G55" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="H55" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="B56" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="D56" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="F56" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="G56" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="H56" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="B57" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="D57" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="F57" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="G57" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="H57" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="B58" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="D58" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="F58" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="G58" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="H58" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="B59" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="D59" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="F59" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="G59" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="H59" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="B60" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="D60" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="F60" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="G60" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="H60" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="B61" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="D61" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="F61" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="G61" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="H61" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="B62" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="D62" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="F62" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="G62" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="H62" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="D63" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="F63" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="G63" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="H63" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="B64" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="D64" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="F64" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="G64" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="H64" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="B65" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="D65" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="F65" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="G65" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="H65" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="B66" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="D66" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="F66" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="G66" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="H66" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="B67" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="D67" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="F67" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="G67" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="H67" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="B68" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="D68" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="F68" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="G68" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="H68" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="B69" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="D69" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="F69" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="G69" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="H69" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="B70" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="D70" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="F70" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="G70" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="H70" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="B71" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="D71" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="F71" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="G71" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="H71" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="B72" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="D72" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="F72" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="G72" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="H72" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="B73" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="D73" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="F73" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="G73" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="H73" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="B74" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="D74" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="F74" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="G74" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="H74" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="B75" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="D75" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="F75" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="G75" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="H75" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="B76" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="D76" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="F76" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="G76" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="H76" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="B77" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="D77" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="F77" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="G77" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="H77" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="B78" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="D78" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="F78" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="G78" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="H78" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="B79" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="D79" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="F79" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="G79" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="H79" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="B80" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="D80" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="F80" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="G80" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="H80" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="B81" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="D81" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="F81" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="G81" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="H81" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="B82" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="D82" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="F82" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="G82" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="H82" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="B83" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="D83" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="F83" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="G83" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="H83" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="B84" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="D84" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="F84" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="G84" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="H84" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="B85" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="D85" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="F85" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="G85" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="H85" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="B86" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="D86" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="F86" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="G86" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="H86" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="B87" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="D87" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="F87" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="G87" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="H87" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="B88" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="D88" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="F88" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="G88" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="H88" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="B89" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="D89" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="F89" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="G89" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="H89" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="B90" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="D90" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="F90" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="G90" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="H90" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="B91" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="D91" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="F91" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="G91" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="H91" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="B92" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="D92" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="F92" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="G92" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="H92" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="B93" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="D93" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I2" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E3" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H3" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C4" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E4" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G4" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H4" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I4" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C5" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E5" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="G5" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="H5" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I5" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C6" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E6" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G6" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="H6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I6" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C7" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="E7" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="G7" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="H7" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="I7" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C8" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E8" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="G8" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="H8" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I8" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C9" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="E9" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="G9" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="H9" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="I9" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C10" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E10" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="G10" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="H10" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I10" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C11" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="E11" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="G11" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="H11" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="I11" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C12" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="E12" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="G12" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="H12" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I12" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C13" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="E13" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="G13" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="H13" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="I13" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C14" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="E14" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="G14" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="H14" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="I14" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C15" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="E15" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="G15" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="H15" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="I15" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C16" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="E16" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="G16" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="H16" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="I16" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C17" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="E17" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="G17" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="H17" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="I17" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C18" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="E18" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="G18" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="H18" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="I18" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C19" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="E19" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="G19" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="H19" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I19" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C20" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="E20" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="G20" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="H20" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I20" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C21" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="E21" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="G21" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="H21" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I21" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C22" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="E22" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="G22" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="H22" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="I22" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C23" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="E23" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="G23" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="H23" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="I23" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C24" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="E24" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="G24" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="H24" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="I24" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C25" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="E25" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="G25" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="H25" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="I25" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C26" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="E26" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="G26" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="H26" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="I26" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C27" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="E27" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="G27" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="H27" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="I27" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C28" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="E28" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="G28" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="H28" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="I28" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C29" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="E29" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="G29" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="H29" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="I29" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C30" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="E30" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="G30" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="H30" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="I30" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C31" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="E31" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="G31" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="H31" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="I31" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C32" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="E32" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="G32" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="H32" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="I32" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C33" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="E33" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="G33" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="H33" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="I33" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C34" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="E34" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="G34" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="H34" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="I34" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C35" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="E35" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="G35" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="H35" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="I35" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C36" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="E36" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="G36" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="H36" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="I36" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C37" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="E37" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="G37" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="H37" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="I37" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C38" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="E38" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="G38" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="H38" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="I38" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C39" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="E39" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="G39" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="H39" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="I39" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C40" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="E40" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="G40" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="H40" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="I40" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C41" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="E41" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="G41" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="H41" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="I41" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C42" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="E42" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="G42" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="H42" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="I42" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C43" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="E43" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="G43" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="H43" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="I43" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C44" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="E44" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="G44" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="H44" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="I44" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C45" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="E45" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="G45" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="H45" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="I45" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C46" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="E46" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="G46" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="H46" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="I46" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C47" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="E47" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="G47" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="H47" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="I47" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C48" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="E48" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="G48" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="H48" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="I48" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C49" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="E49" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="G49" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="H49" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="I49" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C50" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="E50" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="G50" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="H50" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="I50" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C51" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="E51" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="G51" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="H51" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="I51" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C52" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="E52" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="G52" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="H52" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="I52" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C53" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="E53" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="G53" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="H53" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="I53" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C54" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="E54" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="G54" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="H54" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="I54" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C55" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="E55" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="G55" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="H55" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="I55" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C56" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="E56" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="G56" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="H56" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="I56" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C57" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="E57" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="G57" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="H57" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="I57" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C58" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="E58" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="G58" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="H58" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="I58" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C59" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="E59" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="G59" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="H59" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="I59" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C60" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="E60" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="G60" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="H60" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="I60" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C61" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="E61" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="G61" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="H61" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="I61" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C62" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="E62" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="G62" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="H62" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="I62" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="E63" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="G63" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="H63" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="I63" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C64" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="E64" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="G64" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="H64" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="I64" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C65" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="E65" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="G65" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="H65" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="I65" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C66" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="E66" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="G66" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="H66" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="I66" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C67" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="E67" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="G67" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="H67" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="I67" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C68" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="E68" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="G68" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="H68" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="I68" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C69" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="E69" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="G69" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="H69" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="I69" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C70" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="E70" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="G70" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="H70" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="I70" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C71" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="E71" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="G71" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="H71" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="I71" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C72" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="E72" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="G72" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="H72" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="I72" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C73" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="E73" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="G73" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="H73" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="I73" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C74" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="E74" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="G74" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="H74" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="I74" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C75" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="E75" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="G75" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="H75" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="I75" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C76" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="E76" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="G76" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="H76" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="I76" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C77" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="E77" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="G77" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="H77" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="I77" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C78" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="E78" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="G78" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="H78" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="I78" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C79" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="E79" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="G79" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="H79" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="I79" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C80" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="E80" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="G80" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="H80" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="I80" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C81" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="E81" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="G81" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="H81" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="I81" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C82" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="E82" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="G82" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="H82" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="I82" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C83" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="E83" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="G83" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="H83" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="I83" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C84" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="E84" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="G84" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="H84" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="I84" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C85" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="E85" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="G85" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="H85" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="I85" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C86" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="E86" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="G86" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="H86" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="I86" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C87" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="E87" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="G87" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="H87" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="I87" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C88" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="E88" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="G88" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="H88" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="I88" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C89" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="E89" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="G89" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="H89" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="I89" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C90" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="E90" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="G90" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="H90" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="I90" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C91" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="E91" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="G91" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="H91" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="I91" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C92" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="E92" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="G92" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="H92" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="I92" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C93" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="E93" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId457"/>
 </worksheet>
 </file>